--- a/artfynd/A 7955-2023 artfynd.xlsx
+++ b/artfynd/A 7955-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7955-2023 artfynd.xlsx
+++ b/artfynd/A 7955-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,124 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7246590</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83001</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nybygget, Lennartsnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>654373</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6592027</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kungsängen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-04-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-04-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>340m syd om Nybygget. På väggmossa i ganska gles brukad granskog med tall. Troligen snart avverkningsbar.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7955-2023 artfynd.xlsx
+++ b/artfynd/A 7955-2023 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>7246590</v>
       </c>
       <c r="B2" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
